--- a/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0002T0006Z000C1N68_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0002T0006Z000C1N68_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>76.03616791140593</v>
+        <v>12.35587728560346</v>
       </c>
       <c r="D2" t="n">
-        <v>77.15315649452475</v>
+        <v>12.53738793036027</v>
       </c>
       <c r="E2" t="n">
-        <v>23.18633700009661</v>
+        <v>3.767779762515699</v>
       </c>
       <c r="F2" t="n">
-        <v>23.13214182360201</v>
+        <v>3.758973046335327</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>66.06445975195653</v>
+        <v>10.73547470969294</v>
       </c>
       <c r="D3" t="n">
-        <v>67.10955618426036</v>
+        <v>10.90530287994231</v>
       </c>
       <c r="E3" t="n">
-        <v>23.18633700009661</v>
+        <v>3.767779762515699</v>
       </c>
       <c r="F3" t="n">
-        <v>23.13214182360201</v>
+        <v>3.758973046335327</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>11.10858339104789</v>
+        <v>1.805144801045282</v>
       </c>
       <c r="D4" t="n">
-        <v>11.31470897722006</v>
+        <v>1.838640208798259</v>
       </c>
       <c r="E4" t="n">
-        <v>23.18633700009661</v>
+        <v>3.767779762515699</v>
       </c>
       <c r="F4" t="n">
-        <v>23.13214182360201</v>
+        <v>3.758973046335327</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>79.54755755356057</v>
+        <v>12.92647810245359</v>
       </c>
       <c r="D5" t="n">
-        <v>80.6608168262963</v>
+        <v>13.10738273427315</v>
       </c>
       <c r="E5" t="n">
-        <v>23.18633700009661</v>
+        <v>3.767779762515699</v>
       </c>
       <c r="F5" t="n">
-        <v>23.13214182360201</v>
+        <v>3.758973046335327</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>69.57046737760656</v>
+        <v>11.30520094886107</v>
       </c>
       <c r="D6" t="n">
-        <v>70.63180823941835</v>
+        <v>11.47766883890548</v>
       </c>
       <c r="E6" t="n">
-        <v>23.18633700009661</v>
+        <v>3.767779762515699</v>
       </c>
       <c r="F6" t="n">
-        <v>23.13214182360201</v>
+        <v>3.758973046335327</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>85.27934911563098</v>
+        <v>13.85789423129003</v>
       </c>
       <c r="D7" t="n">
-        <v>84.22241406973407</v>
+        <v>13.68614228633179</v>
       </c>
       <c r="E7" t="n">
-        <v>23.18633700009661</v>
+        <v>3.767779762515699</v>
       </c>
       <c r="F7" t="n">
-        <v>23.13214182360201</v>
+        <v>3.758973046335327</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>75.0292315384947</v>
+        <v>12.19225012500539</v>
       </c>
       <c r="D8" t="n">
-        <v>73.89909775152876</v>
+        <v>12.00860338462342</v>
       </c>
       <c r="E8" t="n">
-        <v>23.18633700009661</v>
+        <v>3.767779762515699</v>
       </c>
       <c r="F8" t="n">
-        <v>23.13214182360201</v>
+        <v>3.758973046335327</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
